--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/21.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/21.xlsx
@@ -426,13 +426,13 @@
         <v>-13.60416649164257</v>
       </c>
       <c r="E2">
-        <v>-11.83477355257142</v>
+        <v>-14.47979602332437</v>
       </c>
       <c r="F2">
-        <v>3.92925211180218</v>
+        <v>1.33948402532514</v>
       </c>
       <c r="G2">
-        <v>-16.84549344930944</v>
+        <v>-15.0041457321756</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.43687200510562</v>
       </c>
       <c r="E3">
-        <v>-11.80146895095762</v>
+        <v>-14.76520885877792</v>
       </c>
       <c r="F3">
-        <v>4.024542527615819</v>
+        <v>1.341912798550149</v>
       </c>
       <c r="G3">
-        <v>-15.63648373661078</v>
+        <v>-14.35592265227579</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.21023128311169</v>
       </c>
       <c r="E4">
-        <v>-11.97162186572452</v>
+        <v>-15.0694814268575</v>
       </c>
       <c r="F4">
-        <v>4.195805831409811</v>
+        <v>1.369767480836685</v>
       </c>
       <c r="G4">
-        <v>-15.67532247852048</v>
+        <v>-13.86700459658111</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.96055369099025</v>
       </c>
       <c r="E5">
-        <v>-12.20840059656432</v>
+        <v>-16.25120710474494</v>
       </c>
       <c r="F5">
-        <v>4.371482676725919</v>
+        <v>1.768700938350899</v>
       </c>
       <c r="G5">
-        <v>-15.69030945784577</v>
+        <v>-13.81647232964782</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.69045658743403</v>
       </c>
       <c r="E6">
-        <v>-12.91528547047279</v>
+        <v>-15.26773496944819</v>
       </c>
       <c r="F6">
-        <v>4.164639336246882</v>
+        <v>2.121764379302493</v>
       </c>
       <c r="G6">
-        <v>-15.33405247243163</v>
+        <v>-13.02259841975439</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.43138894725275</v>
       </c>
       <c r="E7">
-        <v>-12.94075296231664</v>
+        <v>-17.26515550474328</v>
       </c>
       <c r="F7">
-        <v>3.975975346789684</v>
+        <v>1.919617881997329</v>
       </c>
       <c r="G7">
-        <v>-15.14510505413899</v>
+        <v>-13.4516899577714</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.18768531647449</v>
       </c>
       <c r="E8">
-        <v>-14.21959733382386</v>
+        <v>-17.53049586986393</v>
       </c>
       <c r="F8">
-        <v>4.437597992612958</v>
+        <v>2.065118959564257</v>
       </c>
       <c r="G8">
-        <v>-13.19866834035136</v>
+        <v>-13.07551821261626</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.976523268817</v>
       </c>
       <c r="E9">
-        <v>-13.90501649523605</v>
+        <v>-18.55521770003888</v>
       </c>
       <c r="F9">
-        <v>4.481602525784474</v>
+        <v>2.223970006194701</v>
       </c>
       <c r="G9">
-        <v>-12.78404163274141</v>
+        <v>-12.36027601369027</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.80153168062306</v>
       </c>
       <c r="E10">
-        <v>-14.95069542975608</v>
+        <v>-18.76482196918032</v>
       </c>
       <c r="F10">
-        <v>5.106874122235208</v>
+        <v>2.771336961881753</v>
       </c>
       <c r="G10">
-        <v>-13.18089700191966</v>
+        <v>-11.92236146432759</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.66340467307963</v>
       </c>
       <c r="E11">
-        <v>-15.4596507115572</v>
+        <v>-19.51572672992065</v>
       </c>
       <c r="F11">
-        <v>4.641538733712586</v>
+        <v>3.218264369979365</v>
       </c>
       <c r="G11">
-        <v>-12.28102947237162</v>
+        <v>-12.06990638952206</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.56823017386783</v>
       </c>
       <c r="E12">
-        <v>-16.69075807209685</v>
+        <v>-20.2175073071109</v>
       </c>
       <c r="F12">
-        <v>5.413693124558117</v>
+        <v>2.983102461468224</v>
       </c>
       <c r="G12">
-        <v>-10.82793211024372</v>
+        <v>-11.27234741363827</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.50202276445871</v>
       </c>
       <c r="E13">
-        <v>-16.6925065740646</v>
+        <v>-20.70062130804893</v>
       </c>
       <c r="F13">
-        <v>5.130991210800313</v>
+        <v>3.707826191564261</v>
       </c>
       <c r="G13">
-        <v>-11.21226765373527</v>
+        <v>-11.17031951501756</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.47037301947181</v>
       </c>
       <c r="E14">
-        <v>-18.32398350631772</v>
+        <v>-21.09064523035225</v>
       </c>
       <c r="F14">
-        <v>5.42421339057367</v>
+        <v>4.08983278956967</v>
       </c>
       <c r="G14">
-        <v>-10.29996906381665</v>
+        <v>-10.90056302476849</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.44832240728525</v>
       </c>
       <c r="E15">
-        <v>-19.3601515869039</v>
+        <v>-22.07024657269426</v>
       </c>
       <c r="F15">
-        <v>6.19205033051581</v>
+        <v>3.742277991846693</v>
       </c>
       <c r="G15">
-        <v>-11.23519912885132</v>
+        <v>-10.68641800505471</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.4343713463195</v>
       </c>
       <c r="E16">
-        <v>-20.64657972229026</v>
+        <v>-22.50093458707898</v>
       </c>
       <c r="F16">
-        <v>6.351295680029987</v>
+        <v>4.03083646314229</v>
       </c>
       <c r="G16">
-        <v>-9.459369352603765</v>
+        <v>-10.22357998245297</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.39966246963776</v>
       </c>
       <c r="E17">
-        <v>-19.42088814931819</v>
+        <v>-23.35202726460815</v>
       </c>
       <c r="F17">
-        <v>5.865509557067051</v>
+        <v>4.101814295683762</v>
       </c>
       <c r="G17">
-        <v>-9.350635756500784</v>
+        <v>-10.05912265379727</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.34377015101755</v>
       </c>
       <c r="E18">
-        <v>-20.94819008191064</v>
+        <v>-24.24193585517916</v>
       </c>
       <c r="F18">
-        <v>6.716638839360682</v>
+        <v>4.385568236043122</v>
       </c>
       <c r="G18">
-        <v>-8.703051003653497</v>
+        <v>-10.15211215464354</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.24597890136982</v>
       </c>
       <c r="E19">
-        <v>-21.98666734799341</v>
+        <v>-24.75944259909809</v>
       </c>
       <c r="F19">
-        <v>6.293238722237382</v>
+        <v>4.518123587839098</v>
       </c>
       <c r="G19">
-        <v>-8.485012058382081</v>
+        <v>-9.719144966281016</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.11495130926036</v>
       </c>
       <c r="E20">
-        <v>-21.87036912447557</v>
+        <v>-25.20648180646867</v>
       </c>
       <c r="F20">
-        <v>6.774886321655932</v>
+        <v>4.547588616356677</v>
       </c>
       <c r="G20">
-        <v>-8.274281892593486</v>
+        <v>-9.251213380982009</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.94388181735666</v>
       </c>
       <c r="E21">
-        <v>-22.76052690772607</v>
+        <v>-26.75023876233008</v>
       </c>
       <c r="F21">
-        <v>7.684201787057005</v>
+        <v>5.003321569946047</v>
       </c>
       <c r="G21">
-        <v>-7.662921220947896</v>
+        <v>-8.994588936026231</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.7501685676522</v>
       </c>
       <c r="E22">
-        <v>-23.15991216835555</v>
+        <v>-26.37439390348973</v>
       </c>
       <c r="F22">
-        <v>7.028494315492612</v>
+        <v>5.0383714514933</v>
       </c>
       <c r="G22">
-        <v>-8.186113131634702</v>
+        <v>-8.243975064007547</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.53975486309177</v>
       </c>
       <c r="E23">
-        <v>-23.77661005834537</v>
+        <v>-27.30529468983679</v>
       </c>
       <c r="F23">
-        <v>7.098247821012746</v>
+        <v>4.696104951269795</v>
       </c>
       <c r="G23">
-        <v>-8.568172105842812</v>
+        <v>-8.199035011988418</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.32812640003283</v>
       </c>
       <c r="E24">
-        <v>-22.82362249417286</v>
+        <v>-26.99441851575073</v>
       </c>
       <c r="F24">
-        <v>7.646699937997465</v>
+        <v>4.938939198665664</v>
       </c>
       <c r="G24">
-        <v>-6.656707621225447</v>
+        <v>-7.938063677288438</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.12661842319274</v>
       </c>
       <c r="E25">
-        <v>-24.85519488619202</v>
+        <v>-28.57837855723649</v>
       </c>
       <c r="F25">
-        <v>7.056955362717997</v>
+        <v>5.295904250084444</v>
       </c>
       <c r="G25">
-        <v>-7.665219981560371</v>
+        <v>-8.165480417131134</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.93925383224262</v>
       </c>
       <c r="E26">
-        <v>-23.74628330925147</v>
+        <v>-27.83486651265436</v>
       </c>
       <c r="F26">
-        <v>7.884282336059586</v>
+        <v>5.275098974395732</v>
       </c>
       <c r="G26">
-        <v>-8.082035798509972</v>
+        <v>-7.982703493679589</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.777867159933768</v>
       </c>
       <c r="E27">
-        <v>-24.15744707719817</v>
+        <v>-28.57994224130028</v>
       </c>
       <c r="F27">
-        <v>6.851611367238028</v>
+        <v>5.118787702222271</v>
       </c>
       <c r="G27">
-        <v>-7.273639621828472</v>
+        <v>-7.783758228975278</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.634953861856021</v>
       </c>
       <c r="E28">
-        <v>-24.22041806730522</v>
+        <v>-29.40117125279827</v>
       </c>
       <c r="F28">
-        <v>6.928903016123638</v>
+        <v>5.130515727911106</v>
       </c>
       <c r="G28">
-        <v>-6.640711589115695</v>
+        <v>-7.496526719805586</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.522181943955824</v>
       </c>
       <c r="E29">
-        <v>-23.51379899892154</v>
+        <v>-28.90353139525165</v>
       </c>
       <c r="F29">
-        <v>6.899663303539621</v>
+        <v>5.171529854758515</v>
       </c>
       <c r="G29">
-        <v>-6.407488553302364</v>
+        <v>-7.153686350845181</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.427290466504409</v>
       </c>
       <c r="E30">
-        <v>-23.45590323305343</v>
+        <v>-28.99006355320445</v>
       </c>
       <c r="F30">
-        <v>7.196024995769589</v>
+        <v>5.092656024133557</v>
       </c>
       <c r="G30">
-        <v>-6.246230692143069</v>
+        <v>-6.971881929753825</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.361180511485577</v>
       </c>
       <c r="E31">
-        <v>-24.9650930110583</v>
+        <v>-29.53532620840722</v>
       </c>
       <c r="F31">
-        <v>7.349453549381308</v>
+        <v>5.490408229731379</v>
       </c>
       <c r="G31">
-        <v>-7.084256209189114</v>
+        <v>-6.849025510785216</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.311273714430387</v>
       </c>
       <c r="E32">
-        <v>-23.59135606720139</v>
+        <v>-29.10186177225185</v>
       </c>
       <c r="F32">
-        <v>7.934087097785504</v>
+        <v>4.972378733981874</v>
       </c>
       <c r="G32">
-        <v>-7.208767840228488</v>
+        <v>-7.112073692807426</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.288669337815863</v>
       </c>
       <c r="E33">
-        <v>-25.2353756976555</v>
+        <v>-29.42946085173734</v>
       </c>
       <c r="F33">
-        <v>7.221770654648598</v>
+        <v>5.153014186571141</v>
       </c>
       <c r="G33">
-        <v>-6.310413237170998</v>
+        <v>-6.682010957802516</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.28168398193897</v>
       </c>
       <c r="E34">
-        <v>-24.1616335142136</v>
+        <v>-29.43331295524112</v>
       </c>
       <c r="F34">
-        <v>7.121713812799251</v>
+        <v>5.189248633504397</v>
       </c>
       <c r="G34">
-        <v>-6.550523417215687</v>
+        <v>-6.42971121126192</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.30049197854779</v>
       </c>
       <c r="E35">
-        <v>-23.36065763774114</v>
+        <v>-28.31670340111</v>
       </c>
       <c r="F35">
-        <v>7.221649713007789</v>
+        <v>5.281270311546588</v>
       </c>
       <c r="G35">
-        <v>-6.483053944747547</v>
+        <v>-6.629788233746478</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.334211293253237</v>
       </c>
       <c r="E36">
-        <v>-25.08699806986467</v>
+        <v>-28.32509081138049</v>
       </c>
       <c r="F36">
-        <v>6.934940157755241</v>
+        <v>5.292705095174832</v>
       </c>
       <c r="G36">
-        <v>-6.847944662524495</v>
+        <v>-6.928520072840024</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.390014769331996</v>
       </c>
       <c r="E37">
-        <v>-22.40537750091733</v>
+        <v>-27.93111718510726</v>
       </c>
       <c r="F37">
-        <v>7.641724763376252</v>
+        <v>5.288806798177258</v>
       </c>
       <c r="G37">
-        <v>-7.124600045355588</v>
+        <v>-6.543296876187486</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.460777252233113</v>
       </c>
       <c r="E38">
-        <v>-22.57379022013913</v>
+        <v>-28.38232621664795</v>
       </c>
       <c r="F38">
-        <v>7.567975213505012</v>
+        <v>5.602691774446046</v>
       </c>
       <c r="G38">
-        <v>-7.501048529437394</v>
+        <v>-7.014938329550465</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.546886410434844</v>
       </c>
       <c r="E39">
-        <v>-21.34020339243855</v>
+        <v>-27.62333930666951</v>
       </c>
       <c r="F39">
-        <v>7.560153768487779</v>
+        <v>5.884243914248765</v>
       </c>
       <c r="G39">
-        <v>-7.471565390769952</v>
+        <v>-6.835650666244942</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.647406926569756</v>
       </c>
       <c r="E40">
-        <v>-22.03658894811785</v>
+        <v>-27.12650724872557</v>
       </c>
       <c r="F40">
-        <v>7.605647706249528</v>
+        <v>6.059316051360829</v>
       </c>
       <c r="G40">
-        <v>-6.919821071862435</v>
+        <v>-7.112992674903498</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.756233187018331</v>
       </c>
       <c r="E41">
-        <v>-22.19334775636218</v>
+        <v>-26.11679512427856</v>
       </c>
       <c r="F41">
-        <v>7.499306869282544</v>
+        <v>5.875027498525218</v>
       </c>
       <c r="G41">
-        <v>-7.607867144382794</v>
+        <v>-6.986144427455077</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.878621330749541</v>
       </c>
       <c r="E42">
-        <v>-20.48453802924075</v>
+        <v>-27.00977293801862</v>
       </c>
       <c r="F42">
-        <v>7.177900316996336</v>
+        <v>6.02872941337986</v>
       </c>
       <c r="G42">
-        <v>-7.58851108398428</v>
+        <v>-7.658900674277581</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.00366819165563</v>
       </c>
       <c r="E43">
-        <v>-21.49537152074547</v>
+        <v>-25.8446434925852</v>
       </c>
       <c r="F43">
-        <v>7.315253572789327</v>
+        <v>6.053946573855883</v>
       </c>
       <c r="G43">
-        <v>-7.817345458139951</v>
+        <v>-7.792770519303802</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.13892606616043</v>
       </c>
       <c r="E44">
-        <v>-20.03920163851336</v>
+        <v>-26.47584024330999</v>
       </c>
       <c r="F44">
-        <v>7.915193694062452</v>
+        <v>6.140469549078291</v>
       </c>
       <c r="G44">
-        <v>-7.762382757635539</v>
+        <v>-7.966573008223396</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.27010645981689</v>
       </c>
       <c r="E45">
-        <v>-20.35276909353792</v>
+        <v>-25.56271935464451</v>
       </c>
       <c r="F45">
-        <v>7.507058731437942</v>
+        <v>6.196062942214971</v>
       </c>
       <c r="G45">
-        <v>-7.382716530845185</v>
+        <v>-7.774338662490542</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.40458001880034</v>
       </c>
       <c r="E46">
-        <v>-20.27276163057642</v>
+        <v>-24.5424705330664</v>
       </c>
       <c r="F46">
-        <v>7.440559053076004</v>
+        <v>6.600130620891737</v>
       </c>
       <c r="G46">
-        <v>-7.68173946796064</v>
+        <v>-9.061662880688818</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.52653960162301</v>
       </c>
       <c r="E47">
-        <v>-18.83487418459621</v>
+        <v>-24.22882416702668</v>
       </c>
       <c r="F47">
-        <v>7.759939418694964</v>
+        <v>6.304093648683666</v>
       </c>
       <c r="G47">
-        <v>-6.809671146818774</v>
+        <v>-8.698647982900585</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.64396782914162</v>
       </c>
       <c r="E48">
-        <v>-19.2613757619655</v>
+        <v>-24.80782335782102</v>
       </c>
       <c r="F48">
-        <v>7.354876042400034</v>
+        <v>5.917131756874711</v>
       </c>
       <c r="G48">
-        <v>-8.656092846065439</v>
+        <v>-8.976925943495054</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.74222107140668</v>
       </c>
       <c r="E49">
-        <v>-18.70728337948615</v>
+        <v>-24.9810164232777</v>
       </c>
       <c r="F49">
-        <v>7.524547224045845</v>
+        <v>6.302566139192904</v>
       </c>
       <c r="G49">
-        <v>-8.387592123964689</v>
+        <v>-8.790510947455793</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.82994806864897</v>
       </c>
       <c r="E50">
-        <v>-18.25757365723371</v>
+        <v>-24.11809955310675</v>
       </c>
       <c r="F50">
-        <v>7.600611232440507</v>
+        <v>6.137762444405943</v>
       </c>
       <c r="G50">
-        <v>-8.326081676025764</v>
+        <v>-8.534958213154669</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.89643543229499</v>
       </c>
       <c r="E51">
-        <v>-17.90842148757803</v>
+        <v>-24.56361037870978</v>
       </c>
       <c r="F51">
-        <v>7.494381396705498</v>
+        <v>6.04504825121501</v>
       </c>
       <c r="G51">
-        <v>-9.087024959019189</v>
+        <v>-9.056740321762275</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.95050567601676</v>
       </c>
       <c r="E52">
-        <v>-16.75705993768641</v>
+        <v>-22.8312893222785</v>
       </c>
       <c r="F52">
-        <v>7.739331294448117</v>
+        <v>6.04048560356039</v>
       </c>
       <c r="G52">
-        <v>-9.096321820508143</v>
+        <v>-9.229484153750171</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.99009752700292</v>
       </c>
       <c r="E53">
-        <v>-18.73008866287078</v>
+        <v>-22.5587472887206</v>
       </c>
       <c r="F53">
-        <v>7.181646194391795</v>
+        <v>6.090938148595297</v>
       </c>
       <c r="G53">
-        <v>-8.651098491662639</v>
+        <v>-9.293483946656723</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.01798897399661</v>
       </c>
       <c r="E54">
-        <v>-16.66389094803653</v>
+        <v>-22.44757412797759</v>
       </c>
       <c r="F54">
-        <v>7.001986558603027</v>
+        <v>6.134117627833625</v>
       </c>
       <c r="G54">
-        <v>-8.914167559641578</v>
+        <v>-9.178666010284152</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.039804482081</v>
       </c>
       <c r="E55">
-        <v>-16.46003472336865</v>
+        <v>-22.28474332477636</v>
       </c>
       <c r="F55">
-        <v>6.963450907024795</v>
+        <v>6.005437378747944</v>
       </c>
       <c r="G55">
-        <v>-8.873233695197513</v>
+        <v>-9.426075832205594</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.05127935686502</v>
       </c>
       <c r="E56">
-        <v>-16.64567080995451</v>
+        <v>-20.69336149465313</v>
       </c>
       <c r="F56">
-        <v>6.966423089266039</v>
+        <v>6.041373613416192</v>
       </c>
       <c r="G56">
-        <v>-9.984420113439445</v>
+        <v>-9.407792787834028</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.06410160524817</v>
       </c>
       <c r="E57">
-        <v>-17.37763692705362</v>
+        <v>-21.85721590420983</v>
       </c>
       <c r="F57">
-        <v>6.888130772557846</v>
+        <v>6.092321522157973</v>
       </c>
       <c r="G57">
-        <v>-9.80312087142647</v>
+        <v>-9.085160887381134</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.0692150688653</v>
       </c>
       <c r="E58">
-        <v>-15.7296842054749</v>
+        <v>-21.33892835656183</v>
       </c>
       <c r="F58">
-        <v>7.079198684217969</v>
+        <v>6.133831012712256</v>
       </c>
       <c r="G58">
-        <v>-10.00152571200042</v>
+        <v>-9.641848651171925</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.07929024435763</v>
       </c>
       <c r="E59">
-        <v>-16.4066825706899</v>
+        <v>-20.87752734443</v>
       </c>
       <c r="F59">
-        <v>6.581885000477675</v>
+        <v>5.837959713984746</v>
       </c>
       <c r="G59">
-        <v>-9.871156875470882</v>
+        <v>-9.184574125293841</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.08220404566639</v>
       </c>
       <c r="E60">
-        <v>-15.60131259663577</v>
+        <v>-21.08061107179147</v>
       </c>
       <c r="F60">
-        <v>7.386110463689992</v>
+        <v>6.073486104153117</v>
       </c>
       <c r="G60">
-        <v>-10.38098177385119</v>
+        <v>-9.834465470987375</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.09022393291342</v>
       </c>
       <c r="E61">
-        <v>-15.34415821103636</v>
+        <v>-20.39768192080461</v>
       </c>
       <c r="F61">
-        <v>7.246262165279768</v>
+        <v>6.426372274480513</v>
       </c>
       <c r="G61">
-        <v>-9.791334664969888</v>
+        <v>-9.685277082072798</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.0905501210938</v>
       </c>
       <c r="E62">
-        <v>-14.63485201492552</v>
+        <v>-20.14945693955358</v>
       </c>
       <c r="F62">
-        <v>6.88804296561315</v>
+        <v>6.054516490629009</v>
       </c>
       <c r="G62">
-        <v>-9.993113892927852</v>
+        <v>-10.2165205290786</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.0951545895959</v>
       </c>
       <c r="E63">
-        <v>-14.23703666817682</v>
+        <v>-20.01952787646765</v>
       </c>
       <c r="F63">
-        <v>7.118370521961552</v>
+        <v>6.026600509154665</v>
       </c>
       <c r="G63">
-        <v>-10.09470318645725</v>
+        <v>-10.01132122570628</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.09254296706574</v>
       </c>
       <c r="E64">
-        <v>-14.88195978233017</v>
+        <v>-20.39283927639986</v>
       </c>
       <c r="F64">
-        <v>6.907562615092718</v>
+        <v>5.923152331158257</v>
       </c>
       <c r="G64">
-        <v>-10.81065028642284</v>
+        <v>-10.18816523207452</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.09299261929921</v>
       </c>
       <c r="E65">
-        <v>-12.82891944097298</v>
+        <v>-19.96035707472282</v>
       </c>
       <c r="F65">
-        <v>7.207835858198704</v>
+        <v>5.866251774259959</v>
       </c>
       <c r="G65">
-        <v>-10.15905412451131</v>
+        <v>-9.975410433855513</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.0880978924017</v>
       </c>
       <c r="E66">
-        <v>-13.65009238411808</v>
+        <v>-20.54870929742068</v>
       </c>
       <c r="F66">
-        <v>7.142661567681245</v>
+        <v>6.427508794557153</v>
       </c>
       <c r="G66">
-        <v>-10.51233486109158</v>
+        <v>-10.79092350029239</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.0821966213192</v>
       </c>
       <c r="E67">
-        <v>-14.86480701955863</v>
+        <v>-20.76420282022073</v>
       </c>
       <c r="F67">
-        <v>7.295723982900927</v>
+        <v>5.860938625738403</v>
       </c>
       <c r="G67">
-        <v>-9.874112238348022</v>
+        <v>-9.727392308444342</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.07302159520629</v>
       </c>
       <c r="E68">
-        <v>-13.718009848913</v>
+        <v>-19.9728665472332</v>
       </c>
       <c r="F68">
-        <v>6.18832764740763</v>
+        <v>6.190854167986168</v>
       </c>
       <c r="G68">
-        <v>-10.21828539242219</v>
+        <v>-10.50339958772849</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.05730313403159</v>
       </c>
       <c r="E69">
-        <v>-13.65522160010424</v>
+        <v>-20.0493437805686</v>
       </c>
       <c r="F69">
-        <v>6.77819979126713</v>
+        <v>6.324352201886531</v>
       </c>
       <c r="G69">
-        <v>-10.81393199237387</v>
+        <v>-10.31867765955657</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.03997363550503</v>
       </c>
       <c r="E70">
-        <v>-14.61054742225262</v>
+        <v>-18.75079242132505</v>
       </c>
       <c r="F70">
-        <v>7.101526499193027</v>
+        <v>6.319671926060714</v>
       </c>
       <c r="G70">
-        <v>-9.902057648451299</v>
+        <v>-10.34353194806396</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.01112795132673</v>
       </c>
       <c r="E71">
-        <v>-14.61465079504156</v>
+        <v>-19.40158402308039</v>
       </c>
       <c r="F71">
-        <v>7.157656674406722</v>
+        <v>6.211835057564274</v>
       </c>
       <c r="G71">
-        <v>-9.744292963554914</v>
+        <v>-10.85924538086953</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.98099947634142</v>
       </c>
       <c r="E72">
-        <v>-15.97589903244471</v>
+        <v>-19.56114624896897</v>
       </c>
       <c r="F72">
-        <v>7.023843860893295</v>
+        <v>6.060177553459741</v>
       </c>
       <c r="G72">
-        <v>-9.578227416231085</v>
+        <v>-10.71340135577617</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.93754799831001</v>
       </c>
       <c r="E73">
-        <v>-16.68860670863059</v>
+        <v>-20.09360870686861</v>
       </c>
       <c r="F73">
-        <v>6.484420948599091</v>
+        <v>6.398920178751736</v>
       </c>
       <c r="G73">
-        <v>-9.787267124896934</v>
+        <v>-10.62137391431172</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.89260662465159</v>
       </c>
       <c r="E74">
-        <v>-15.83154586642764</v>
+        <v>-19.08765523867057</v>
       </c>
       <c r="F74">
-        <v>6.932229739613281</v>
+        <v>6.4182609008723</v>
       </c>
       <c r="G74">
-        <v>-10.37429435158105</v>
+        <v>-10.98174021171227</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.83491267513288</v>
       </c>
       <c r="E75">
-        <v>-14.73680089331609</v>
+        <v>-19.45079127085695</v>
       </c>
       <c r="F75">
-        <v>6.762010178746817</v>
+        <v>6.354209876553036</v>
       </c>
       <c r="G75">
-        <v>-9.537643391562229</v>
+        <v>-11.0651052026234</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.77657800165706</v>
       </c>
       <c r="E76">
-        <v>-16.16691768090755</v>
+        <v>-20.3906380743977</v>
       </c>
       <c r="F76">
-        <v>6.666000740027548</v>
+        <v>6.483518028130039</v>
       </c>
       <c r="G76">
-        <v>-10.19049662699438</v>
+        <v>-11.07775817628423</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.70555480469707</v>
       </c>
       <c r="E77">
-        <v>-16.10907590678666</v>
+        <v>-20.70704217275712</v>
       </c>
       <c r="F77">
-        <v>6.882323917064222</v>
+        <v>6.596585208407755</v>
       </c>
       <c r="G77">
-        <v>-9.191241966979545</v>
+        <v>-10.68174738298121</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.6293721084702</v>
       </c>
       <c r="E78">
-        <v>-15.45770285544585</v>
+        <v>-20.90531232819311</v>
       </c>
       <c r="F78">
-        <v>6.374818000799882</v>
+        <v>6.329834337358258</v>
       </c>
       <c r="G78">
-        <v>-9.529482203970408</v>
+        <v>-10.48561519557383</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.53441398928032</v>
       </c>
       <c r="E79">
-        <v>-15.8913396498712</v>
+        <v>-20.43931786433602</v>
       </c>
       <c r="F79">
-        <v>6.67270057558139</v>
+        <v>6.550064095066535</v>
       </c>
       <c r="G79">
-        <v>-8.742742153672193</v>
+        <v>-10.09788437874152</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.42232922522164</v>
       </c>
       <c r="E80">
-        <v>-17.6111512337921</v>
+        <v>-20.53455515322566</v>
       </c>
       <c r="F80">
-        <v>7.085477709131189</v>
+        <v>6.390296874088594</v>
       </c>
       <c r="G80">
-        <v>-8.889375929004366</v>
+        <v>-9.876806526766051</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.28316444249044</v>
       </c>
       <c r="E81">
-        <v>-17.79876424896858</v>
+        <v>-21.31995233401869</v>
       </c>
       <c r="F81">
-        <v>7.426536449681413</v>
+        <v>6.461475171541545</v>
       </c>
       <c r="G81">
-        <v>-8.913043634095104</v>
+        <v>-10.23703314933098</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.11386005284655</v>
       </c>
       <c r="E82">
-        <v>-19.29495447552674</v>
+        <v>-22.38427503417588</v>
       </c>
       <c r="F82">
-        <v>6.884762630698064</v>
+        <v>6.346554105016363</v>
       </c>
       <c r="G82">
-        <v>-8.937226961242587</v>
+        <v>-9.849727883867024</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.914138140710525</v>
       </c>
       <c r="E83">
-        <v>-18.23934936594037</v>
+        <v>-23.17704416507047</v>
       </c>
       <c r="F83">
-        <v>6.575784902923459</v>
+        <v>6.691019092326899</v>
       </c>
       <c r="G83">
-        <v>-8.48145491887669</v>
+        <v>-9.486527623212822</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.679085220851823</v>
       </c>
       <c r="E84">
-        <v>-20.93222929078932</v>
+        <v>-24.00827203283298</v>
       </c>
       <c r="F84">
-        <v>6.644312424687451</v>
+        <v>5.948962602694684</v>
       </c>
       <c r="G84">
-        <v>-8.439313585059233</v>
+        <v>-8.979206428895392</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.418678712997757</v>
       </c>
       <c r="E85">
-        <v>-20.30190056123142</v>
+        <v>-24.95843956651593</v>
       </c>
       <c r="F85">
-        <v>6.957697067044949</v>
+        <v>6.407092851547757</v>
       </c>
       <c r="G85">
-        <v>-9.110375458642107</v>
+        <v>-9.3808903701949</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.127873429212691</v>
       </c>
       <c r="E86">
-        <v>-23.83132861754999</v>
+        <v>-26.04813838786782</v>
       </c>
       <c r="F86">
-        <v>6.913222021188644</v>
+        <v>6.974020875084516</v>
       </c>
       <c r="G86">
-        <v>-8.187064748038164</v>
+        <v>-8.362442821318494</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.823174507813036</v>
       </c>
       <c r="E87">
-        <v>-24.44354103930899</v>
+        <v>-26.92447013061797</v>
       </c>
       <c r="F87">
-        <v>7.302299563344349</v>
+        <v>6.315538372720744</v>
       </c>
       <c r="G87">
-        <v>-8.815233393361341</v>
+        <v>-8.636140230527856</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.501530582645364</v>
       </c>
       <c r="E88">
-        <v>-25.51082497914078</v>
+        <v>-28.40436938575448</v>
       </c>
       <c r="F88">
-        <v>7.460098583373238</v>
+        <v>7.017356087394569</v>
       </c>
       <c r="G88">
-        <v>-7.764442635117927</v>
+        <v>-8.550127944601332</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.178797731833068</v>
       </c>
       <c r="E89">
-        <v>-25.13125053653072</v>
+        <v>-29.03588801035695</v>
       </c>
       <c r="F89">
-        <v>6.857428163140486</v>
+        <v>6.80256704678788</v>
       </c>
       <c r="G89">
-        <v>-7.149433447906257</v>
+        <v>-8.325359805146322</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.850578313851954</v>
       </c>
       <c r="E90">
-        <v>-30.17281299768346</v>
+        <v>-30.15468007703926</v>
       </c>
       <c r="F90">
-        <v>7.225915805132207</v>
+        <v>7.054248258045648</v>
       </c>
       <c r="G90">
-        <v>-6.820936509729428</v>
+        <v>-7.936736113663858</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.527487791411185</v>
       </c>
       <c r="E91">
-        <v>-29.1689984333177</v>
+        <v>-31.51836417288443</v>
       </c>
       <c r="F91">
-        <v>6.986827435131796</v>
+        <v>6.676421601954766</v>
       </c>
       <c r="G91">
-        <v>-6.362293953685602</v>
+        <v>-7.304287152583551</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.202783757063636</v>
       </c>
       <c r="E92">
-        <v>-31.64159410610342</v>
+        <v>-32.96681738847501</v>
       </c>
       <c r="F92">
-        <v>6.656018912823813</v>
+        <v>6.636756057239114</v>
       </c>
       <c r="G92">
-        <v>-6.881740751256456</v>
+        <v>-7.612553430923843</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.880911985752759</v>
       </c>
       <c r="E93">
-        <v>-33.2178395575533</v>
+        <v>-34.7700399920381</v>
       </c>
       <c r="F93">
-        <v>6.833690466845863</v>
+        <v>6.931711181619129</v>
       </c>
       <c r="G93">
-        <v>-6.475239986186344</v>
+        <v>-7.819421000089886</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.555056601336275</v>
       </c>
       <c r="E94">
-        <v>-35.84043676375785</v>
+        <v>-37.02801639300763</v>
       </c>
       <c r="F94">
-        <v>6.864038535014826</v>
+        <v>6.762419392243799</v>
       </c>
       <c r="G94">
-        <v>-7.177728697784743</v>
+        <v>-7.318272911358144</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.226259197920997</v>
       </c>
       <c r="E95">
-        <v>-36.1252577665976</v>
+        <v>-39.3772803788969</v>
       </c>
       <c r="F95">
-        <v>7.24384830266801</v>
+        <v>6.666370191889197</v>
       </c>
       <c r="G95">
-        <v>-5.707853385542052</v>
+        <v>-7.068615238343754</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.893747166372496</v>
       </c>
       <c r="E96">
-        <v>-40.21801910059327</v>
+        <v>-40.70230015391357</v>
       </c>
       <c r="F96">
-        <v>6.223319543236687</v>
+        <v>7.057952717070967</v>
       </c>
       <c r="G96">
-        <v>-6.076699381374537</v>
+        <v>-6.706732098335769</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.558773869624086</v>
       </c>
       <c r="E97">
-        <v>-42.07686358682412</v>
+        <v>-43.89185431467612</v>
       </c>
       <c r="F97">
-        <v>6.038285459738555</v>
+        <v>6.79991295762931</v>
       </c>
       <c r="G97">
-        <v>-5.464059444879302</v>
+        <v>-6.920961967248751</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.230940808537733</v>
       </c>
       <c r="E98">
-        <v>-43.51795108213012</v>
+        <v>-45.39555770052089</v>
       </c>
       <c r="F98">
-        <v>6.1450288832633</v>
+        <v>6.839611637041074</v>
       </c>
       <c r="G98">
-        <v>-6.069629485021802</v>
+        <v>-6.841381250622436</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.915435881639862</v>
       </c>
       <c r="E99">
-        <v>-47.04670008839708</v>
+        <v>-46.97791460243527</v>
       </c>
       <c r="F99">
-        <v>6.307970408128768</v>
+        <v>6.650505299390781</v>
       </c>
       <c r="G99">
-        <v>-6.100853990331517</v>
+        <v>-7.145389404534622</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.631373035426406</v>
       </c>
       <c r="E100">
-        <v>-48.11196972073633</v>
+        <v>-49.29962826100128</v>
       </c>
       <c r="F100">
-        <v>6.00735090744841</v>
+        <v>6.347097514032599</v>
       </c>
       <c r="G100">
-        <v>-5.511744694835986</v>
+        <v>-6.453466376296459</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.387715305738571</v>
       </c>
       <c r="E101">
-        <v>-51.33882491070999</v>
+        <v>-50.71291312139604</v>
       </c>
       <c r="F101">
-        <v>5.162164332902464</v>
+        <v>6.47465615365489</v>
       </c>
       <c r="G101">
-        <v>-6.288292398250495</v>
+        <v>-6.604495340147772</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.203278864299111</v>
       </c>
       <c r="E102">
-        <v>-52.35489456339249</v>
+        <v>-53.38645361771093</v>
       </c>
       <c r="F102">
-        <v>4.930425238499691</v>
+        <v>6.423295717946515</v>
       </c>
       <c r="G102">
-        <v>-5.556140406607867</v>
+        <v>-6.800050553000522</v>
       </c>
     </row>
   </sheetData>
